--- a/src/templates/import/PC.xlsx
+++ b/src/templates/import/PC.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\ITAMS\itams-system\src\templates\import\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\app-infra\src\templates\import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1FC05A4-77BC-497B-AFF5-6B601F2CA811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4EC3003-3A77-4E8C-87A5-7A91D9FA6A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="71">
   <si>
     <t>ACC</t>
   </si>
@@ -238,9 +238,6 @@
   </si>
   <si>
     <t>note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INVENTORY PC INFORMATION DAIHOA 06/2025												</t>
   </si>
 </sst>
 </file>
@@ -250,7 +247,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0_);\(0\)"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -321,14 +318,6 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -350,7 +339,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -373,15 +362,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -390,7 +370,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -421,9 +401,6 @@
     </xf>
     <xf numFmtId="1" fontId="10" fillId="2" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -746,7 +723,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.42578125" style="2" customWidth="1"/>
@@ -758,83 +735,101 @@
     <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-    </row>
-    <row r="2" spans="1:11" ht="15.75">
-      <c r="A2" s="11" t="s">
+    <row r="1" spans="1:11" ht="15.75">
+      <c r="A1" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B1" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D1" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E1" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F1" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G1" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H1" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I1" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J1" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="K1" s="11" t="s">
         <v>70</v>
       </c>
+    </row>
+    <row r="2" spans="1:11" ht="46.5" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="10">
+        <v>514000000121</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="10">
+        <v>900000000448</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="10">
+        <v>900000000501</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="4"/>
     </row>
     <row r="3" spans="1:11" ht="46.5" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="10">
-        <v>514000000121</v>
+        <v>514000000093</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E3" s="10">
-        <v>900000000448</v>
+        <v>900000000449</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G3" s="10">
-        <v>900000000501</v>
+        <v>900000000500</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>15</v>
@@ -846,28 +841,28 @@
         <v>0</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="10">
-        <v>514000000093</v>
+        <v>514000000161</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E4" s="10">
-        <v>900000000449</v>
+        <v>900000000446</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G4" s="10">
-        <v>900000000500</v>
+        <v>900000000499</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>15</v>
@@ -879,28 +874,28 @@
         <v>0</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" s="10">
-        <v>514000000161</v>
+        <v>514000000162</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" s="10">
-        <v>900000000446</v>
+        <v>900000000442</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G5" s="10">
-        <v>900000000499</v>
+        <v>900000000465</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>15</v>
@@ -912,28 +907,28 @@
         <v>0</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="10">
-        <v>514000000162</v>
+        <v>514000000163</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6" s="10">
-        <v>900000000442</v>
+        <v>900000000444</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G6" s="10">
-        <v>900000000465</v>
+        <v>900000000497</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>15</v>
@@ -945,28 +940,28 @@
         <v>0</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="10">
-        <v>514000000163</v>
+        <v>514000000164</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E7" s="10">
-        <v>900000000444</v>
+        <v>900000001655</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G7" s="10">
-        <v>900000000497</v>
+        <v>900000000502</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>15</v>
@@ -978,28 +973,26 @@
         <v>0</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="10">
-        <v>514000000164</v>
+        <v>900000000418</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E8" s="10">
-        <v>900000001655</v>
+        <v>900000000443</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G8" s="10">
-        <v>900000000502</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>5</v>
-      </c>
+        <v>900000000496</v>
+      </c>
+      <c r="H8" s="5"/>
       <c r="I8" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>15</v>
@@ -1011,26 +1004,28 @@
         <v>0</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" s="10">
-        <v>900000000418</v>
+        <v>514000000092</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E9" s="10">
-        <v>900000000443</v>
+        <v>900000001656</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G9" s="10">
-        <v>900000000496</v>
-      </c>
-      <c r="H9" s="5"/>
+        <v>900000000504</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="I9" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>15</v>
@@ -1042,92 +1037,92 @@
         <v>0</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="C10" s="10">
-        <v>514000000092</v>
+        <v>900000000480</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="10">
-        <v>900000001656</v>
+        <v>52</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>52</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G10" s="10">
-        <v>900000000504</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K10" s="4"/>
+        <v>900000000503</v>
+      </c>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" s="9"/>
     </row>
     <row r="11" spans="1:11" ht="46.5" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="C11" s="10">
-        <v>900000000480</v>
+        <v>514000000091</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>52</v>
+        <v>36</v>
+      </c>
+      <c r="E11" s="10">
+        <v>900000001613</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G11" s="10">
-        <v>900000000503</v>
-      </c>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="K11" s="9"/>
+        <v>900000001509</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K11" s="4"/>
     </row>
     <row r="12" spans="1:11" ht="46.5" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" s="10">
-        <v>514000000091</v>
+        <v>514000000032</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E12" s="10">
-        <v>900000001613</v>
+        <v>900000000445</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G12" s="10">
-        <v>900000001509</v>
+        <v>900000000498</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>15</v>
@@ -1139,86 +1134,62 @@
         <v>0</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C13" s="10">
-        <v>514000000032</v>
+        <v>514000000051</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E13" s="10">
-        <v>900000000445</v>
+        <v>900000000451</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="G13" s="10">
-        <v>900000000498</v>
+        <v>52</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>52</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K13" s="4"/>
     </row>
-    <row r="14" spans="1:11" ht="46.5" customHeight="1">
-      <c r="A14" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="10">
-        <v>514000000051</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="10">
-        <v>900000000451</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K14" s="4"/>
+    <row r="14" spans="1:11" ht="23.25" customHeight="1">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
     </row>
     <row r="15" spans="1:11" ht="23.25" customHeight="1">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
+      <c r="D15" s="8"/>
       <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
     </row>
     <row r="16" spans="1:11" ht="23.25" customHeight="1">
       <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="6"/>
-      <c r="G16" s="7"/>
+      <c r="B16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="6"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
     </row>
     <row r="17" spans="1:10" ht="23.25" customHeight="1">
       <c r="A17" s="6"/>
@@ -1229,8 +1200,7 @@
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
     </row>
-    <row r="18" spans="1:10" ht="23.25" customHeight="1">
-      <c r="A18" s="6"/>
+    <row r="18" spans="1:10" ht="15.75">
       <c r="B18" s="8"/>
       <c r="E18" s="8"/>
       <c r="F18" s="6"/>
@@ -1238,18 +1208,7 @@
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
     </row>
-    <row r="19" spans="1:10" ht="15.75">
-      <c r="B19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="6"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
-  </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="43" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/src/templates/import/PC.xlsx
+++ b/src/templates/import/PC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\app-infra\src\templates\import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4EC3003-3A77-4E8C-87A5-7A91D9FA6A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF719C9B-161B-49F0-8CA5-AA45EE833D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Acc" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="72">
   <si>
     <t>ACC</t>
   </si>
@@ -210,27 +210,6 @@
     <t>Dept</t>
   </si>
   <si>
-    <t>CPU_barcode</t>
-  </si>
-  <si>
-    <t>CPU_SAP_barcode</t>
-  </si>
-  <si>
-    <t>Monitor_barcode</t>
-  </si>
-  <si>
-    <t>Monitor_SAP_barcode</t>
-  </si>
-  <si>
-    <t>UPS_barcode</t>
-  </si>
-  <si>
-    <t>UPS_SAP_barcode</t>
-  </si>
-  <si>
-    <t>PC_Name</t>
-  </si>
-  <si>
     <t>user</t>
   </si>
   <si>
@@ -238,6 +217,30 @@
   </si>
   <si>
     <t>note</t>
+  </si>
+  <si>
+    <t>CPUBarcode</t>
+  </si>
+  <si>
+    <t>CPUSAPBarcode</t>
+  </si>
+  <si>
+    <t>MonitorBarcode</t>
+  </si>
+  <si>
+    <t>MonitorSAPBarcode</t>
+  </si>
+  <si>
+    <t>UPSBarcode</t>
+  </si>
+  <si>
+    <t>UPSSAPBarcode</t>
+  </si>
+  <si>
+    <t>PCName</t>
+  </si>
+  <si>
+    <t>SGDH-NA</t>
   </si>
 </sst>
 </file>
@@ -740,34 +743,34 @@
         <v>60</v>
       </c>
       <c r="B1" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="J1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="K1" s="11" t="s">
         <v>63</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="K1" s="11" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="46.5" customHeight="1">
@@ -990,7 +993,9 @@
       <c r="G8" s="10">
         <v>900000000496</v>
       </c>
-      <c r="H8" s="5"/>
+      <c r="H8" s="5" t="s">
+        <v>71</v>
+      </c>
       <c r="I8" s="1" t="s">
         <v>12</v>
       </c>
@@ -1054,7 +1059,9 @@
       <c r="G10" s="10">
         <v>900000000503</v>
       </c>
-      <c r="H10" s="9"/>
+      <c r="H10" s="5" t="s">
+        <v>71</v>
+      </c>
       <c r="I10" s="9" t="s">
         <v>14</v>
       </c>
